--- a/TEXTRADE/TEXTRADE/DOCUMENTATION/SWPL/YARNSTOCK/YARN JOBBER STOCK.xlsx
+++ b/TEXTRADE/TEXTRADE/DOCUMENTATION/SWPL/YARNSTOCK/YARN JOBBER STOCK.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32424456-EA2A-4A24-BC84-4E84142B56EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0589FF-97BD-4E68-BBE6-C74B0AAD3F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,14 +17,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>DENIER/COUNT</t>
   </si>
   <si>
-    <t>BALANCE(KG)</t>
-  </si>
-  <si>
     <t>450 ATY</t>
   </si>
   <si>
@@ -43,9 +40,6 @@
     <t>SHREE SHAKTI ENTERPRISE</t>
   </si>
   <si>
-    <t>JOBBER NAME</t>
-  </si>
-  <si>
     <t>VARDHMAN</t>
   </si>
   <si>
@@ -70,9 +64,6 @@
     <t>LOTNO</t>
   </si>
   <si>
-    <t>MILLNAME</t>
-  </si>
-  <si>
     <t>BAGS</t>
   </si>
   <si>
@@ -89,6 +80,51 @@
   </si>
   <si>
     <t>MIX</t>
+  </si>
+  <si>
+    <t>YARN QUALITY</t>
+  </si>
+  <si>
+    <t>MILL NAME</t>
+  </si>
+  <si>
+    <t>DESIGN</t>
+  </si>
+  <si>
+    <t>COLOR</t>
+  </si>
+  <si>
+    <t>BOX/LR NO</t>
+  </si>
+  <si>
+    <t>PARTYNAME</t>
+  </si>
+  <si>
+    <t>GODOWN</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>CONES</t>
+  </si>
+  <si>
+    <t>RACK</t>
+  </si>
+  <si>
+    <t>GRIDREMARKS</t>
+  </si>
+  <si>
+    <t>RATE</t>
+  </si>
+  <si>
+    <t>HSNCODE</t>
+  </si>
+  <si>
+    <t>BARCODE</t>
+  </si>
+  <si>
+    <t>CATEGRY</t>
   </si>
 </sst>
 </file>
@@ -113,12 +149,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -141,19 +177,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -460,225 +511,288 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1027.867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>651.04999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>233.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>54.43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1538.39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>78.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>513</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2">
+        <v>64</v>
+      </c>
+      <c r="J8" s="2">
+        <v>3101.6320000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>491</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2">
+        <v>134</v>
+      </c>
+      <c r="J9" s="2">
+        <v>6090.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>492</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2">
+        <v>175</v>
+      </c>
+      <c r="J10" s="2">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>140022</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="I11" s="2">
+        <v>38</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>140404</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1027.867</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2">
-        <v>651.04999999999995</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2">
-        <v>233.38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>54.43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1538.39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3">
-        <v>78.12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3101.6320000000001</v>
-      </c>
-      <c r="D8" s="3">
-        <v>513</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3">
-        <v>6090.8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>491</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3">
-        <v>7938</v>
-      </c>
-      <c r="D10" s="3">
-        <v>492</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1776</v>
-      </c>
-      <c r="D11" s="3">
-        <v>140022</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2">
+        <v>99</v>
+      </c>
+      <c r="J12" s="2">
         <v>5000.8</v>
-      </c>
-      <c r="D12" s="3">
-        <v>140404</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="3">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
